--- a/artfynd/A 23597-2021 artfynd.xlsx
+++ b/artfynd/A 23597-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118922123</v>
+        <v>118922022</v>
       </c>
       <c r="B2" t="n">
-        <v>94620</v>
+        <v>108721</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>220299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554628</v>
+        <v>554631</v>
       </c>
       <c r="R2" t="n">
-        <v>6343990</v>
+        <v>6343981</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118922057</v>
+        <v>118922111</v>
       </c>
       <c r="B3" t="n">
-        <v>96807</v>
+        <v>91786</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554655</v>
+        <v>554649</v>
       </c>
       <c r="R3" t="n">
-        <v>6343921</v>
+        <v>6343923</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118922111</v>
+        <v>118922124</v>
       </c>
       <c r="B4" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>554649</v>
+        <v>554652</v>
       </c>
       <c r="R4" t="n">
-        <v>6343923</v>
+        <v>6343958</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118922022</v>
+        <v>118922051</v>
       </c>
       <c r="B5" t="n">
-        <v>108714</v>
+        <v>96808</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,20 +993,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>554631</v>
+        <v>554651</v>
       </c>
       <c r="R5" t="n">
-        <v>6343981</v>
+        <v>6343893</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
         <v>118922063</v>
       </c>
       <c r="B6" t="n">
-        <v>88095</v>
+        <v>88102</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>118922074</v>
       </c>
       <c r="B7" t="n">
-        <v>91204</v>
+        <v>91211</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,10 +1286,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118922051</v>
+        <v>118922057</v>
       </c>
       <c r="B8" t="n">
-        <v>96801</v>
+        <v>96814</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1302,16 +1302,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1326,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>554651</v>
+        <v>554655</v>
       </c>
       <c r="R8" t="n">
-        <v>6343893</v>
+        <v>6343921</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118922124</v>
+        <v>118922123</v>
       </c>
       <c r="B9" t="n">
-        <v>91773</v>
+        <v>94627</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1400,25 +1400,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>554652</v>
+        <v>554628</v>
       </c>
       <c r="R9" t="n">
-        <v>6343958</v>
+        <v>6343990</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 23597-2021 artfynd.xlsx
+++ b/artfynd/A 23597-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118922022</v>
+        <v>118922123</v>
       </c>
       <c r="B2" t="n">
-        <v>108721</v>
+        <v>94627</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220299</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554631</v>
+        <v>554628</v>
       </c>
       <c r="R2" t="n">
-        <v>6343981</v>
+        <v>6343990</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118922111</v>
+        <v>118922074</v>
       </c>
       <c r="B3" t="n">
-        <v>91786</v>
+        <v>91211</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Moråns ravin, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554649</v>
+        <v>554620</v>
       </c>
       <c r="R3" t="n">
-        <v>6343923</v>
+        <v>6343997</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -861,6 +859,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -879,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118922124</v>
+        <v>118922111</v>
       </c>
       <c r="B4" t="n">
-        <v>91780</v>
+        <v>91786</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +890,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>554652</v>
+        <v>554649</v>
       </c>
       <c r="R4" t="n">
-        <v>6343958</v>
+        <v>6343923</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1083,10 +1082,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118922063</v>
+        <v>118922124</v>
       </c>
       <c r="B6" t="n">
-        <v>88102</v>
+        <v>91780</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1098,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4962</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>554648</v>
+        <v>554652</v>
       </c>
       <c r="R6" t="n">
-        <v>6343960</v>
+        <v>6343958</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1185,10 +1184,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118922074</v>
+        <v>118922057</v>
       </c>
       <c r="B7" t="n">
-        <v>91211</v>
+        <v>96814</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,36 +1196,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>757</v>
+        <v>221941</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Moråns ravin, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>554620</v>
+        <v>554655</v>
       </c>
       <c r="R7" t="n">
-        <v>6343997</v>
+        <v>6343921</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1267,7 +1268,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1286,10 +1286,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118922057</v>
+        <v>118922022</v>
       </c>
       <c r="B8" t="n">
-        <v>96814</v>
+        <v>108721</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1298,20 +1298,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1326,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>554655</v>
+        <v>554631</v>
       </c>
       <c r="R8" t="n">
-        <v>6343921</v>
+        <v>6343981</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118922123</v>
+        <v>118922063</v>
       </c>
       <c r="B9" t="n">
-        <v>94627</v>
+        <v>88102</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1400,25 +1400,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>4962</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>554628</v>
+        <v>554648</v>
       </c>
       <c r="R9" t="n">
-        <v>6343990</v>
+        <v>6343960</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
